--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9CAA1D5-DF5F-4B78-A168-35F417847462}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{672A7227-9137-4A03-9CA0-BF333624952C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,6 +20,9 @@
     <sheet name="data_mercado_corp" sheetId="5" r:id="rId5"/>
     <sheet name="data_sae_corp" sheetId="6" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_corp!$A$1:$H$219</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="40">
   <si>
     <t>UNIDAD_ACADEMICA</t>
   </si>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -6175,6 +6178,266 @@
       </c>
       <c r="H219">
         <v>0.77464788732394396</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>18</v>
+      </c>
+      <c r="B220">
+        <v>2024</v>
+      </c>
+      <c r="C220" t="s">
+        <v>8</v>
+      </c>
+      <c r="D220">
+        <v>35</v>
+      </c>
+      <c r="E220">
+        <v>20</v>
+      </c>
+      <c r="F220">
+        <v>2</v>
+      </c>
+      <c r="G220">
+        <v>43</v>
+      </c>
+      <c r="H220">
+        <v>0.86046511627906996</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>18</v>
+      </c>
+      <c r="B221">
+        <v>2024</v>
+      </c>
+      <c r="C221" t="s">
+        <v>10</v>
+      </c>
+      <c r="D221">
+        <v>40</v>
+      </c>
+      <c r="E221">
+        <v>16</v>
+      </c>
+      <c r="F221">
+        <v>0</v>
+      </c>
+      <c r="G221">
+        <v>59</v>
+      </c>
+      <c r="H221">
+        <v>0.677966101694915</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>18</v>
+      </c>
+      <c r="B222">
+        <v>2024</v>
+      </c>
+      <c r="C222" t="s">
+        <v>9</v>
+      </c>
+      <c r="D222">
+        <v>57</v>
+      </c>
+      <c r="E222">
+        <v>15</v>
+      </c>
+      <c r="F222">
+        <v>2</v>
+      </c>
+      <c r="G222">
+        <v>74</v>
+      </c>
+      <c r="H222">
+        <v>0.79729729729729704</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>18</v>
+      </c>
+      <c r="B223">
+        <v>2024</v>
+      </c>
+      <c r="C223" t="s">
+        <v>11</v>
+      </c>
+      <c r="D223">
+        <v>56</v>
+      </c>
+      <c r="E223">
+        <v>10</v>
+      </c>
+      <c r="F223">
+        <v>1</v>
+      </c>
+      <c r="G223">
+        <v>69</v>
+      </c>
+      <c r="H223">
+        <v>0.82608695652173902</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>18</v>
+      </c>
+      <c r="B224">
+        <v>2024</v>
+      </c>
+      <c r="C224" t="s">
+        <v>13</v>
+      </c>
+      <c r="D224">
+        <v>55</v>
+      </c>
+      <c r="E224">
+        <v>16</v>
+      </c>
+      <c r="F224">
+        <v>0</v>
+      </c>
+      <c r="G224">
+        <v>65</v>
+      </c>
+      <c r="H224">
+        <v>0.84615384615384603</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>18</v>
+      </c>
+      <c r="B225">
+        <v>2024</v>
+      </c>
+      <c r="C225" t="s">
+        <v>14</v>
+      </c>
+      <c r="D225">
+        <v>55</v>
+      </c>
+      <c r="E225">
+        <v>18</v>
+      </c>
+      <c r="F225">
+        <v>1</v>
+      </c>
+      <c r="G225">
+        <v>66</v>
+      </c>
+      <c r="H225">
+        <v>0.84848484848484795</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>18</v>
+      </c>
+      <c r="B226">
+        <v>2024</v>
+      </c>
+      <c r="C226" t="s">
+        <v>16</v>
+      </c>
+      <c r="D226">
+        <v>58</v>
+      </c>
+      <c r="E226">
+        <v>28</v>
+      </c>
+      <c r="F226">
+        <v>0</v>
+      </c>
+      <c r="G226">
+        <v>71</v>
+      </c>
+      <c r="H226">
+        <v>0.81690140845070403</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>18</v>
+      </c>
+      <c r="B227">
+        <v>2024</v>
+      </c>
+      <c r="C227" t="s">
+        <v>15</v>
+      </c>
+      <c r="D227">
+        <v>75</v>
+      </c>
+      <c r="E227">
+        <v>14</v>
+      </c>
+      <c r="F227">
+        <v>0</v>
+      </c>
+      <c r="G227">
+        <v>90</v>
+      </c>
+      <c r="H227">
+        <v>0.83333333333333404</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>18</v>
+      </c>
+      <c r="B228">
+        <v>2024</v>
+      </c>
+      <c r="C228" t="s">
+        <v>12</v>
+      </c>
+      <c r="D228">
+        <v>22</v>
+      </c>
+      <c r="E228">
+        <v>11</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="G228">
+        <v>26</v>
+      </c>
+      <c r="H228">
+        <v>0.88461538461538403</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>18</v>
+      </c>
+      <c r="B229">
+        <v>2024</v>
+      </c>
+      <c r="C229" t="s">
+        <v>17</v>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>47</v>
+      </c>
+      <c r="F229">
+        <v>1</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{672A7227-9137-4A03-9CA0-BF333624952C}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0C2838B-BCD0-4CA9-AB34-DEAFEA167CFB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <sheet name="data_sae_corp" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_corp!$A$1:$H$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_corp!$A$1:$H$229</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -208,6 +208,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2779,25 +2783,25 @@
         <v>18</v>
       </c>
       <c r="B89">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C89" t="s">
         <v>8</v>
       </c>
       <c r="D89">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F89">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G89">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H89">
-        <v>0.82352941176470595</v>
+        <v>0.86046511627906996</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -2805,25 +2809,25 @@
         <v>18</v>
       </c>
       <c r="B90">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C90" t="s">
         <v>10</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F90">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H90">
-        <v>0.91228070175438603</v>
+        <v>0.677966101694915</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -2831,25 +2835,25 @@
         <v>18</v>
       </c>
       <c r="B91">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C91" t="s">
         <v>9</v>
       </c>
       <c r="D91">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F91">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G91">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H91">
-        <v>0.82142857142857095</v>
+        <v>0.79729729729729704</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -2857,25 +2861,25 @@
         <v>18</v>
       </c>
       <c r="B92">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C92" t="s">
         <v>11</v>
       </c>
       <c r="D92">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E92">
+        <v>10</v>
+      </c>
+      <c r="F92">
         <v>1</v>
       </c>
-      <c r="F92">
-        <v>12</v>
-      </c>
       <c r="G92">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H92">
-        <v>0.86486486486486502</v>
+        <v>0.82608695652173902</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -2883,25 +2887,25 @@
         <v>18</v>
       </c>
       <c r="B93">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C93" t="s">
         <v>13</v>
       </c>
       <c r="D93">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F93">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H93">
-        <v>0.89552238805970197</v>
+        <v>0.84615384615384603</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -2909,25 +2913,25 @@
         <v>18</v>
       </c>
       <c r="B94">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
       </c>
       <c r="D94">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F94">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G94">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H94">
-        <v>0.84507042253521103</v>
+        <v>0.84848484848484795</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -2935,25 +2939,25 @@
         <v>18</v>
       </c>
       <c r="B95">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C95" t="s">
         <v>16</v>
       </c>
       <c r="D95">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="F95">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G95">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H95">
-        <v>0.85135135135135098</v>
+        <v>0.81690140845070403</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -2961,7 +2965,7 @@
         <v>18</v>
       </c>
       <c r="B96">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C96" t="s">
         <v>15</v>
@@ -2970,16 +2974,16 @@
         <v>75</v>
       </c>
       <c r="E96">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="F96">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G96">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H96">
-        <v>0.88372093023255804</v>
+        <v>0.83333333333333404</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -2987,25 +2991,25 @@
         <v>18</v>
       </c>
       <c r="B97">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C97" t="s">
         <v>12</v>
       </c>
       <c r="D97">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F97">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G97">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="H97">
-        <v>0.85416666666666596</v>
+        <v>0.88461538461538403</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -3013,25 +3017,25 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C98" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D98">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G98">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="H98">
-        <v>0.89473684210526305</v>
+        <v>0.82352941176470595</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -3039,25 +3043,25 @@
         <v>18</v>
       </c>
       <c r="B99">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D99">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G99">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="H99">
-        <v>0.92857142857142905</v>
+        <v>0.91228070175438603</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -3065,25 +3069,25 @@
         <v>18</v>
       </c>
       <c r="B100">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C100" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D100">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G100">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H100">
-        <v>0.95081967213114804</v>
+        <v>0.82142857142857095</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -3091,25 +3095,25 @@
         <v>18</v>
       </c>
       <c r="B101">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C101" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D101">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101">
         <v>12</v>
       </c>
       <c r="G101">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H101">
-        <v>0.91666666666666596</v>
+        <v>0.86486486486486502</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -3117,25 +3121,25 @@
         <v>18</v>
       </c>
       <c r="B102">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D102">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
       <c r="F102">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G102">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H102">
-        <v>0.80952380952380998</v>
+        <v>0.89552238805970197</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -3143,25 +3147,25 @@
         <v>18</v>
       </c>
       <c r="B103">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C103" t="s">
+        <v>14</v>
+      </c>
+      <c r="D103">
+        <v>60</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
         <v>10</v>
       </c>
-      <c r="D103">
-        <v>35</v>
-      </c>
-      <c r="E103">
-        <v>1</v>
-      </c>
-      <c r="F103">
-        <v>7</v>
-      </c>
       <c r="G103">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="H103">
-        <v>0.94736842105263197</v>
+        <v>0.84507042253521103</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -3169,13 +3173,13 @@
         <v>18</v>
       </c>
       <c r="B104">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D104">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E104">
         <v>1</v>
@@ -3184,10 +3188,10 @@
         <v>18</v>
       </c>
       <c r="G104">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H104">
-        <v>0.87654320987654299</v>
+        <v>0.85135135135135098</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -3195,25 +3199,25 @@
         <v>18</v>
       </c>
       <c r="B105">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C105" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D105">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G105">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="H105">
-        <v>0.83636363636363598</v>
+        <v>0.88372093023255804</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -3221,25 +3225,25 @@
         <v>18</v>
       </c>
       <c r="B106">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C106" t="s">
         <v>12</v>
       </c>
       <c r="D106">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G106">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H106">
-        <v>0.875</v>
+        <v>0.85416666666666596</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -3247,25 +3251,25 @@
         <v>18</v>
       </c>
       <c r="B107">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C107" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="E107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>0.89473684210526305</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -3273,25 +3277,25 @@
         <v>18</v>
       </c>
       <c r="B108">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C108" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>0.92857142857142905</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -3299,25 +3303,25 @@
         <v>18</v>
       </c>
       <c r="B109">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C109" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>0.95081967213114804</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -3325,25 +3329,25 @@
         <v>18</v>
       </c>
       <c r="B110">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C110" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H110">
-        <v>0</v>
+        <v>0.91666666666666596</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -3354,282 +3358,282 @@
         <v>2026</v>
       </c>
       <c r="C111" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="G111">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>0.80952380952380998</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B112">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C112" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D112">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="E112">
         <v>1</v>
       </c>
       <c r="F112">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="G112">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="H112">
-        <v>0.83050847457627097</v>
+        <v>0.94736842105263197</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B113">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C113" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D113">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G113">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="H113">
-        <v>0.86138613861386104</v>
+        <v>0.87654320987654299</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B114">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C114" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D114">
-        <v>114</v>
+        <v>46</v>
       </c>
       <c r="E114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F114">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G114">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="H114">
-        <v>0.93495934959349603</v>
+        <v>0.83636363636363598</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B115">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C115" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D115">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G115">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="H115">
-        <v>0.93700787401574803</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B116">
         <v>2021</v>
       </c>
       <c r="C116" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D116">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="G116">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H116">
-        <v>0.93076923076923102</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B117">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C117" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D117">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="E117">
         <v>1</v>
       </c>
       <c r="F117">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G117">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="H117">
-        <v>0.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B118">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C118" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D118">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="E118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F118">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G118">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H118">
-        <v>0.92666666666666597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B119">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="C119" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D119">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F119">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G119">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>0.97604790419161702</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B120">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C120" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D120">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G120">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="H120">
-        <v>0.86734693877550995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B121">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C121" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D121">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F121">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G121">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="H121">
-        <v>0.80582524271844602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -3637,25 +3641,25 @@
         <v>19</v>
       </c>
       <c r="B122">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C122" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D122">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E122">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F122">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G122">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="H122">
-        <v>0.841584158415842</v>
+        <v>0.83050847457627097</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -3663,25 +3667,25 @@
         <v>19</v>
       </c>
       <c r="B123">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C123" t="s">
         <v>10</v>
       </c>
       <c r="D123">
+        <v>87</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>14</v>
+      </c>
+      <c r="G123">
         <v>101</v>
       </c>
-      <c r="E123">
-        <v>5</v>
-      </c>
-      <c r="F123">
-        <v>17</v>
-      </c>
-      <c r="G123">
-        <v>127</v>
-      </c>
       <c r="H123">
-        <v>0.83464566929133899</v>
+        <v>0.86138613861386104</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -3689,25 +3693,25 @@
         <v>19</v>
       </c>
       <c r="B124">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C124" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D124">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G124">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="H124">
-        <v>0.85714285714285698</v>
+        <v>0.93495934959349603</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -3715,25 +3719,25 @@
         <v>19</v>
       </c>
       <c r="B125">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C125" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D125">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="E125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F125">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G125">
         <v>127</v>
       </c>
       <c r="H125">
-        <v>0.79527559055118102</v>
+        <v>0.93700787401574803</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -3741,25 +3745,25 @@
         <v>19</v>
       </c>
       <c r="B126">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C126" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126">
+        <v>121</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
         <v>13</v>
       </c>
-      <c r="D126">
-        <v>107</v>
-      </c>
-      <c r="E126">
-        <v>1</v>
-      </c>
-      <c r="F126">
-        <v>19</v>
-      </c>
       <c r="G126">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H126">
-        <v>0.80597014925373101</v>
+        <v>0.93076923076923102</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -3767,25 +3771,25 @@
         <v>19</v>
       </c>
       <c r="B127">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C127" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D127">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G127">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H127">
-        <v>0.85384615384615403</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -3793,25 +3797,25 @@
         <v>19</v>
       </c>
       <c r="B128">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C128" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D128">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E128">
         <v>1</v>
       </c>
       <c r="F128">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="G128">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="H128">
-        <v>0.91095890410958902</v>
+        <v>0.92666666666666597</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -3819,25 +3823,25 @@
         <v>19</v>
       </c>
       <c r="B129">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C129" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D129">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G129">
-        <v>69</v>
+        <v>167</v>
       </c>
       <c r="H129">
-        <v>0.79710144927536197</v>
+        <v>0.97604790419161702</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -3845,25 +3849,25 @@
         <v>19</v>
       </c>
       <c r="B130">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C130" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D130">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E130">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F130">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G130">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="H130">
-        <v>0.91549295774647899</v>
+        <v>0.86734693877550995</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -3871,25 +3875,25 @@
         <v>19</v>
       </c>
       <c r="B131">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C131" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D131">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F131">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G131">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H131">
-        <v>0.79807692307692302</v>
+        <v>0.80582524271844602</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -3897,25 +3901,25 @@
         <v>19</v>
       </c>
       <c r="B132">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C132" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D132">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E132">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F132">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G132">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="H132">
-        <v>0.822033898305085</v>
+        <v>0.841584158415842</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -3923,25 +3927,25 @@
         <v>19</v>
       </c>
       <c r="B133">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C133" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D133">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E133">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F133">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G133">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H133">
-        <v>0.845528455284553</v>
+        <v>0.83464566929133899</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -3949,25 +3953,25 @@
         <v>19</v>
       </c>
       <c r="B134">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C134" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D134">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G134">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H134">
-        <v>0.88976377952755903</v>
+        <v>0.85714285714285698</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -3975,25 +3979,25 @@
         <v>19</v>
       </c>
       <c r="B135">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C135" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135">
+        <v>100</v>
+      </c>
+      <c r="E135">
+        <v>1</v>
+      </c>
+      <c r="F135">
         <v>13</v>
       </c>
-      <c r="D135">
-        <v>98</v>
-      </c>
-      <c r="E135">
-        <v>0</v>
-      </c>
-      <c r="F135">
-        <v>17</v>
-      </c>
       <c r="G135">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="H135">
-        <v>0.859649122807018</v>
+        <v>0.79527559055118102</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -4001,25 +4005,25 @@
         <v>19</v>
       </c>
       <c r="B136">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C136" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D136">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="E136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G136">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H136">
-        <v>0.90977443609022601</v>
+        <v>0.80597014925373101</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -4027,25 +4031,25 @@
         <v>19</v>
       </c>
       <c r="B137">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C137" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D137">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="E137">
         <v>0</v>
       </c>
       <c r="F137">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G137">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="H137">
-        <v>0.89677419354838706</v>
+        <v>0.85384615384615403</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -4053,25 +4057,25 @@
         <v>19</v>
       </c>
       <c r="B138">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C138" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D138">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="E138">
         <v>1</v>
       </c>
       <c r="F138">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G138">
-        <v>55</v>
+        <v>146</v>
       </c>
       <c r="H138">
-        <v>0.83636363636363598</v>
+        <v>0.91095890410958902</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -4079,25 +4083,25 @@
         <v>19</v>
       </c>
       <c r="B139">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C139" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D139">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F139">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G139">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H139">
-        <v>0.8</v>
+        <v>0.79710144927536197</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -4105,25 +4109,25 @@
         <v>19</v>
       </c>
       <c r="B140">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C140" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D140">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E140">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F140">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="G140">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="H140">
-        <v>0.82524271844660202</v>
+        <v>0.91549295774647899</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -4131,25 +4135,25 @@
         <v>19</v>
       </c>
       <c r="B141">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C141" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D141">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E141">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F141">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G141">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H141">
-        <v>0.841584158415842</v>
+        <v>0.79807692307692302</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -4157,25 +4161,25 @@
         <v>19</v>
       </c>
       <c r="B142">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C142" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D142">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F142">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="G142">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H142">
-        <v>0.83333333333333404</v>
+        <v>0.822033898305085</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -4183,25 +4187,25 @@
         <v>19</v>
       </c>
       <c r="B143">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C143" t="s">
         <v>9</v>
       </c>
       <c r="D143">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="E143">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F143">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G143">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="H143">
-        <v>0.855855855855856</v>
+        <v>0.845528455284553</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -4209,25 +4213,25 @@
         <v>19</v>
       </c>
       <c r="B144">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C144" t="s">
+        <v>14</v>
+      </c>
+      <c r="D144">
+        <v>113</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+      <c r="F144">
         <v>16</v>
       </c>
-      <c r="D144">
-        <v>111</v>
-      </c>
-      <c r="E144">
-        <v>1</v>
-      </c>
-      <c r="F144">
-        <v>20</v>
-      </c>
       <c r="G144">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H144">
-        <v>0.86821705426356599</v>
+        <v>0.88976377952755903</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -4235,25 +4239,25 @@
         <v>19</v>
       </c>
       <c r="B145">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D145">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G145">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H145">
-        <v>0.84347826086956501</v>
+        <v>0.859649122807018</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -4261,25 +4265,25 @@
         <v>19</v>
       </c>
       <c r="B146">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C146" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D146">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="G146">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="H146">
-        <v>0.92156862745098</v>
+        <v>0.90977443609022601</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -4287,25 +4291,25 @@
         <v>19</v>
       </c>
       <c r="B147">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C147" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D147">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G147">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="H147">
-        <v>0.9</v>
+        <v>0.89677419354838706</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -4313,25 +4317,25 @@
         <v>19</v>
       </c>
       <c r="B148">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C148" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D148">
+        <v>45</v>
+      </c>
+      <c r="E148">
+        <v>1</v>
+      </c>
+      <c r="F148">
+        <v>24</v>
+      </c>
+      <c r="G148">
         <v>55</v>
       </c>
-      <c r="E148">
-        <v>8</v>
-      </c>
-      <c r="F148">
-        <v>26</v>
-      </c>
-      <c r="G148">
-        <v>63</v>
-      </c>
       <c r="H148">
-        <v>1</v>
+        <v>0.83636363636363598</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -4339,25 +4343,25 @@
         <v>19</v>
       </c>
       <c r="B149">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C149" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D149">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="E149">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F149">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="G149">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="H149">
-        <v>0.861788617886179</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -4365,25 +4369,25 @@
         <v>19</v>
       </c>
       <c r="B150">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C150" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D150">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="E150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F150">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G150">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="H150">
-        <v>0.76470588235294101</v>
+        <v>0.82524271844660202</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -4391,25 +4395,25 @@
         <v>19</v>
       </c>
       <c r="B151">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C151" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D151">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="E151">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F151">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G151">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="H151">
-        <v>0.81818181818181801</v>
+        <v>0.841584158415842</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -4417,25 +4421,25 @@
         <v>19</v>
       </c>
       <c r="B152">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C152" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D152">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E152">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F152">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G152">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="H152">
-        <v>0.865979381443299</v>
+        <v>0.83333333333333404</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -4443,25 +4447,25 @@
         <v>19</v>
       </c>
       <c r="B153">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C153" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D153">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E153">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F153">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G153">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H153">
-        <v>0.99090909090909096</v>
+        <v>0.855855855855856</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -4469,25 +4473,25 @@
         <v>19</v>
       </c>
       <c r="B154">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C154" t="s">
         <v>16</v>
       </c>
       <c r="D154">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E154">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G154">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="H154">
-        <v>0.92035398230088505</v>
+        <v>0.86821705426356599</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -4495,25 +4499,25 @@
         <v>19</v>
       </c>
       <c r="B155">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C155" t="s">
         <v>14</v>
       </c>
       <c r="D155">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="E155">
         <v>0</v>
       </c>
       <c r="F155">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G155">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="H155">
-        <v>0.92473118279569899</v>
+        <v>0.84347826086956501</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -4521,25 +4525,25 @@
         <v>19</v>
       </c>
       <c r="B156">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C156" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D156">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
       <c r="F156">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G156">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="H156">
-        <v>0.85106382978723405</v>
+        <v>0.92156862745098</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -4547,25 +4551,25 @@
         <v>19</v>
       </c>
       <c r="B157">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C157" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D157">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E157">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F157">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G157">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H157">
-        <v>0.96296296296296302</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -4573,25 +4577,25 @@
         <v>19</v>
       </c>
       <c r="B158">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C158" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D158">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="E158">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F158">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="G158">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="H158">
-        <v>0.95199999999999996</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -4599,25 +4603,25 @@
         <v>19</v>
       </c>
       <c r="B159">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C159" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D159">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="E159">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F159">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G159">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="H159">
-        <v>0.92134831460674205</v>
+        <v>0.861788617886179</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -4625,25 +4629,25 @@
         <v>19</v>
       </c>
       <c r="B160">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C160" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D160">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F160">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G160">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H160">
-        <v>0.88095238095238104</v>
+        <v>0.76470588235294101</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -4651,25 +4655,25 @@
         <v>19</v>
       </c>
       <c r="B161">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C161" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D161">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="E161">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F161">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="G161">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H161">
-        <v>0.93893129770992401</v>
+        <v>0.81818181818181801</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -4677,25 +4681,25 @@
         <v>19</v>
       </c>
       <c r="B162">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C162" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D162">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G162">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="H162">
-        <v>0.86666666666666703</v>
+        <v>0.865979381443299</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -4703,25 +4707,25 @@
         <v>19</v>
       </c>
       <c r="B163">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C163" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D163">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E163">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F163">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G163">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H163">
-        <v>0.891891891891892</v>
+        <v>0.99090909090909096</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -4729,25 +4733,25 @@
         <v>19</v>
       </c>
       <c r="B164">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C164" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D164">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F164">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G164">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="H164">
-        <v>0.89312977099236601</v>
+        <v>0.92035398230088505</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -4755,25 +4759,25 @@
         <v>19</v>
       </c>
       <c r="B165">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C165" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D165">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G165">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="H165">
-        <v>0.91176470588235303</v>
+        <v>0.92473118279569899</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -4781,25 +4785,25 @@
         <v>19</v>
       </c>
       <c r="B166">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C166" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>0.85106382978723405</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -4807,25 +4811,25 @@
         <v>19</v>
       </c>
       <c r="B167">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C167" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E167">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F167">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>0.96296296296296302</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -4833,25 +4837,25 @@
         <v>19</v>
       </c>
       <c r="B168">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C168" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="E168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F168">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>0.95199999999999996</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -4859,25 +4863,25 @@
         <v>19</v>
       </c>
       <c r="B169">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C169" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F169">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>0.92134831460674205</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -4885,25 +4889,25 @@
         <v>19</v>
       </c>
       <c r="B170">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C170" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F170">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>0.88095238095238104</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -4914,282 +4918,282 @@
         <v>2026</v>
       </c>
       <c r="C171" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F171">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>0.93893129770992401</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B172">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C172" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D172">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="E172">
         <v>1</v>
       </c>
       <c r="F172">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="G172">
-        <v>319</v>
+        <v>105</v>
       </c>
       <c r="H172">
-        <v>0.94357366771159878</v>
+        <v>0.86666666666666703</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B173">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C173" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D173">
-        <v>273</v>
+        <v>98</v>
       </c>
       <c r="E173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G173">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="H173">
-        <v>0.89508196721311473</v>
+        <v>0.891891891891892</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B174">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C174" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D174">
-        <v>248</v>
+        <v>117</v>
       </c>
       <c r="E174">
         <v>0</v>
       </c>
       <c r="F174">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G174">
-        <v>257</v>
+        <v>131</v>
       </c>
       <c r="H174">
-        <v>0.96498054474708173</v>
+        <v>0.89312977099236601</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B175">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C175" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="D175">
-        <v>249</v>
+        <v>31</v>
       </c>
       <c r="E175">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F175">
+        <v>10</v>
+      </c>
+      <c r="G175">
         <v>34</v>
       </c>
-      <c r="G175">
-        <v>324</v>
-      </c>
       <c r="H175">
-        <v>0.81481481481481477</v>
+        <v>0.91176470588235303</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B176">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C176" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D176">
-        <v>275</v>
+        <v>0</v>
       </c>
       <c r="E176">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F176">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="G176">
-        <v>297</v>
+        <v>0</v>
       </c>
       <c r="H176">
-        <v>0.93602693602693599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B177">
         <v>2022</v>
       </c>
       <c r="C177" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D177">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="E177">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F177">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G177">
-        <v>335</v>
+        <v>0</v>
       </c>
       <c r="H177">
-        <v>0.84776119402985073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B178">
         <v>2023</v>
       </c>
       <c r="C178" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D178">
-        <v>195</v>
+        <v>0</v>
       </c>
       <c r="E178">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F178">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="G178">
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="H178">
-        <v>0.71480144404332135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B179">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C179" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D179">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="E179">
         <v>0</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="G179">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="H179">
-        <v>0.9088050314465409</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B180">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C180" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D180">
-        <v>243</v>
+        <v>0</v>
       </c>
       <c r="E180">
         <v>0</v>
       </c>
       <c r="F180">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G180">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="H180">
-        <v>0.81543624161073824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B181">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C181" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D181">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="E181">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F181">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G181">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="H181">
-        <v>0.77533039647577096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
@@ -5197,25 +5201,25 @@
         <v>20</v>
       </c>
       <c r="B182">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C182" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D182">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="E182">
         <v>1</v>
       </c>
       <c r="F182">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="G182">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="H182">
-        <v>0.94117647058823528</v>
+        <v>0.94357366771159878</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -5223,25 +5227,25 @@
         <v>20</v>
       </c>
       <c r="B183">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C183" t="s">
         <v>22</v>
       </c>
       <c r="D183">
-        <v>196</v>
+        <v>273</v>
       </c>
       <c r="E183">
         <v>0</v>
       </c>
       <c r="F183">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="G183">
-        <v>227</v>
+        <v>305</v>
       </c>
       <c r="H183">
-        <v>0.86343612334801767</v>
+        <v>0.89508196721311473</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -5249,25 +5253,25 @@
         <v>20</v>
       </c>
       <c r="B184">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="C184" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D184">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E184">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F184">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="G184">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="H184">
-        <v>0.81150159744408945</v>
+        <v>0.96498054474708173</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -5275,25 +5279,25 @@
         <v>20</v>
       </c>
       <c r="B185">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C185" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D185">
-        <v>183</v>
+        <v>249</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F185">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G185">
-        <v>226</v>
+        <v>324</v>
       </c>
       <c r="H185">
-        <v>0.80973451327433632</v>
+        <v>0.81481481481481477</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -5301,25 +5305,25 @@
         <v>20</v>
       </c>
       <c r="B186">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C186" t="s">
         <v>23</v>
       </c>
       <c r="D186">
-        <v>230</v>
+        <v>275</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F186">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G186">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="H186">
-        <v>0.91633466135458164</v>
+        <v>0.93602693602693599</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -5327,25 +5331,25 @@
         <v>20</v>
       </c>
       <c r="B187">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="C187" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D187">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="E187">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F187">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G187">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="H187">
-        <v>0.84045584045584043</v>
+        <v>0.84776119402985073</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -5353,25 +5357,25 @@
         <v>20</v>
       </c>
       <c r="B188">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="C188" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D188">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="E188">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F188">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G188">
-        <v>319</v>
+        <v>277</v>
       </c>
       <c r="H188">
-        <v>0.89655172413793105</v>
+        <v>0.71480144404332135</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -5379,25 +5383,25 @@
         <v>20</v>
       </c>
       <c r="B189">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="C189" t="s">
         <v>23</v>
       </c>
       <c r="D189">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="E189">
+        <v>0</v>
+      </c>
+      <c r="F189">
         <v>1</v>
       </c>
-      <c r="F189">
-        <v>7</v>
-      </c>
       <c r="G189">
-        <v>220</v>
+        <v>318</v>
       </c>
       <c r="H189">
-        <v>0.95454545454545459</v>
+        <v>0.9088050314465409</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -5405,25 +5409,25 @@
         <v>20</v>
       </c>
       <c r="B190">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C190" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D190">
-        <v>0</v>
+        <v>243</v>
       </c>
       <c r="E190">
         <v>0</v>
       </c>
       <c r="F190">
-        <v>324</v>
+        <v>29</v>
       </c>
       <c r="G190">
-        <v>205</v>
+        <v>298</v>
       </c>
       <c r="H190">
-        <v>0.71707317073170729</v>
+        <v>0.81543624161073824</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -5431,25 +5435,25 @@
         <v>20</v>
       </c>
       <c r="B191">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C191" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="E191">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F191">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="G191">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="H191">
-        <v>0.60396039603960394</v>
+        <v>0.77533039647577096</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -5457,25 +5461,25 @@
         <v>20</v>
       </c>
       <c r="B192">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C192" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="E192">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F192">
-        <v>221</v>
+        <v>12</v>
       </c>
       <c r="G192">
-        <v>195</v>
+        <v>272</v>
       </c>
       <c r="H192">
-        <v>0.57948717948717954</v>
+        <v>0.94117647058823528</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -5486,22 +5490,22 @@
         <v>2024</v>
       </c>
       <c r="C193" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D193">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="E193">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F193">
-        <v>308</v>
+        <v>55</v>
       </c>
       <c r="G193">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="H193">
-        <v>0.65865384615384615</v>
+        <v>0.86343612334801767</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -5512,22 +5516,22 @@
         <v>2025</v>
       </c>
       <c r="C194" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="E194">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F194">
-        <v>347</v>
+        <v>65</v>
       </c>
       <c r="G194">
-        <v>189</v>
+        <v>313</v>
       </c>
       <c r="H194">
-        <v>0.74603174603174605</v>
+        <v>0.81150159744408945</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -5535,285 +5539,285 @@
         <v>20</v>
       </c>
       <c r="B195">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C195" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="E195">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F195">
-        <v>407</v>
+        <v>37</v>
       </c>
       <c r="G195">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="H195">
-        <v>0.72826086956521741</v>
+        <v>0.80973451327433632</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B196">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C196" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D196">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="E196">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F196">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G196">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="H196">
-        <v>0.92307692307692302</v>
+        <v>0.91633466135458164</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B197">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="C197" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D197">
-        <v>207</v>
+        <v>292</v>
       </c>
       <c r="E197">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F197">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="G197">
-        <v>233</v>
+        <v>351</v>
       </c>
       <c r="H197">
-        <v>0.90987124463519298</v>
+        <v>0.84045584045584043</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>20</v>
+      </c>
+      <c r="B198">
+        <v>2026</v>
+      </c>
+      <c r="C198" t="s">
+        <v>22</v>
+      </c>
+      <c r="D198">
+        <v>285</v>
+      </c>
+      <c r="E198">
+        <v>1</v>
+      </c>
+      <c r="F198">
         <v>25</v>
       </c>
-      <c r="B198">
-        <v>2021</v>
-      </c>
-      <c r="C198" t="s">
-        <v>23</v>
-      </c>
-      <c r="D198">
-        <v>201</v>
-      </c>
-      <c r="E198">
-        <v>0</v>
-      </c>
-      <c r="F198">
-        <v>5</v>
-      </c>
       <c r="G198">
-        <v>219</v>
+        <v>319</v>
       </c>
       <c r="H198">
-        <v>0.91780821917808197</v>
+        <v>0.89655172413793105</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B199">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="C199" t="s">
         <v>23</v>
       </c>
       <c r="D199">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G199">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="H199">
-        <v>0.91228070175438603</v>
+        <v>0.95454545454545459</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B200">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C200" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D200">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="E200">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F200">
-        <v>27</v>
+        <v>324</v>
       </c>
       <c r="G200">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="H200">
-        <v>0.80930232558139503</v>
+        <v>0.71707317073170729</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B201">
         <v>2022</v>
       </c>
       <c r="C201" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D201">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F201">
-        <v>27</v>
+        <v>270</v>
       </c>
       <c r="G201">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="H201">
-        <v>0.78341013824884798</v>
+        <v>0.60396039603960394</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B202">
         <v>2023</v>
       </c>
       <c r="C202" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D202">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F202">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c r="G202">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H202">
-        <v>0.82587064676616895</v>
+        <v>0.57948717948717954</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B203">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C203" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D203">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F203">
-        <v>43</v>
+        <v>308</v>
       </c>
       <c r="G203">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="H203">
-        <v>0.79916317991631802</v>
+        <v>0.65865384615384615</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B204">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C204" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D204">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F204">
-        <v>5</v>
+        <v>347</v>
       </c>
       <c r="G204">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="H204">
-        <v>0.949238578680203</v>
+        <v>0.74603174603174605</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B205">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C205" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D205">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="E205">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F205">
-        <v>9</v>
+        <v>407</v>
       </c>
       <c r="G205">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="H205">
-        <v>0.93034825870646798</v>
+        <v>0.72826086956521741</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -5821,25 +5825,25 @@
         <v>25</v>
       </c>
       <c r="B206">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C206" t="s">
         <v>21</v>
       </c>
       <c r="D206">
-        <v>140</v>
+        <v>202</v>
       </c>
       <c r="E206">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F206">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G206">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="H206">
-        <v>0.79444444444444395</v>
+        <v>0.92307692307692302</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -5847,25 +5851,25 @@
         <v>25</v>
       </c>
       <c r="B207">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C207" t="s">
         <v>22</v>
       </c>
       <c r="D207">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="E207">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F207">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="G207">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H207">
-        <v>0.80341880341880401</v>
+        <v>0.90987124463519298</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -5873,25 +5877,25 @@
         <v>25</v>
       </c>
       <c r="B208">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="C208" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D208">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="E208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F208">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G208">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="H208">
-        <v>0.82352941176470595</v>
+        <v>0.91780821917808197</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -5899,25 +5903,25 @@
         <v>25</v>
       </c>
       <c r="B209">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C209" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D209">
-        <v>153</v>
+        <v>208</v>
       </c>
       <c r="E209">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F209">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="G209">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="H209">
-        <v>0.86592178770949702</v>
+        <v>0.91228070175438603</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -5925,25 +5929,25 @@
         <v>25</v>
       </c>
       <c r="B210">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="C210" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D210">
-        <v>208</v>
+        <v>169</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F210">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="G210">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="H210">
-        <v>0.93273542600896897</v>
+        <v>0.80930232558139503</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -5951,25 +5955,25 @@
         <v>25</v>
       </c>
       <c r="B211">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="C211" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D211">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E211">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F211">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="G211">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="H211">
-        <v>0.85096153846153799</v>
+        <v>0.78341013824884798</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -5977,25 +5981,25 @@
         <v>25</v>
       </c>
       <c r="B212">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="C212" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D212">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="E212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F212">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="G212">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="H212">
-        <v>0.89252336448598102</v>
+        <v>0.82587064676616895</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -6003,25 +6007,25 @@
         <v>25</v>
       </c>
       <c r="B213">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="C213" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D213">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="E213">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F213">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G213">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="H213">
-        <v>0.92201834862385301</v>
+        <v>0.79916317991631802</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -6029,25 +6033,25 @@
         <v>25</v>
       </c>
       <c r="B214">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="C214" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D214">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="E214">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F214">
-        <v>212</v>
+        <v>5</v>
       </c>
       <c r="G214">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="H214">
-        <v>0.81927710843373502</v>
+        <v>0.949238578680203</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -6055,25 +6059,25 @@
         <v>25</v>
       </c>
       <c r="B215">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C215" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D215">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="E215">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F215">
-        <v>236</v>
+        <v>9</v>
       </c>
       <c r="G215">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="H215">
-        <v>0.72131147540983598</v>
+        <v>0.93034825870646798</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -6081,25 +6085,25 @@
         <v>25</v>
       </c>
       <c r="B216">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C216" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="E216">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F216">
-        <v>175</v>
+        <v>36</v>
       </c>
       <c r="G216">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="H216">
-        <v>0.7</v>
+        <v>0.79444444444444395</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -6110,22 +6114,22 @@
         <v>2024</v>
       </c>
       <c r="C217" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="E217">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F217">
-        <v>201</v>
+        <v>35</v>
       </c>
       <c r="G217">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="H217">
-        <v>0.648484848484848</v>
+        <v>0.80341880341880401</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -6136,22 +6140,22 @@
         <v>2025</v>
       </c>
       <c r="C218" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218">
-        <v>208</v>
+        <v>50</v>
       </c>
       <c r="G218">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="H218">
-        <v>0.73291925465838503</v>
+        <v>0.82352941176470595</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -6159,285 +6163,285 @@
         <v>25</v>
       </c>
       <c r="B219">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C219" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D219">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="E219">
         <v>2</v>
       </c>
       <c r="F219">
-        <v>255</v>
+        <v>59</v>
       </c>
       <c r="G219">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="H219">
-        <v>0.77464788732394396</v>
+        <v>0.86592178770949702</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B220">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C220" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D220">
-        <v>35</v>
+        <v>208</v>
       </c>
       <c r="E220">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F220">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G220">
-        <v>43</v>
+        <v>223</v>
       </c>
       <c r="H220">
-        <v>0.86046511627906996</v>
+        <v>0.93273542600896897</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B221">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C221" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D221">
-        <v>40</v>
+        <v>175</v>
       </c>
       <c r="E221">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F221">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G221">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="H221">
-        <v>0.677966101694915</v>
+        <v>0.85096153846153799</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B222">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C222" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D222">
-        <v>57</v>
+        <v>191</v>
       </c>
       <c r="E222">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F222">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G222">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="H222">
-        <v>0.79729729729729704</v>
+        <v>0.89252336448598102</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B223">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C223" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D223">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="E223">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F223">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="G223">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="H223">
-        <v>0.82608695652173902</v>
+        <v>0.92201834862385301</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B224">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C224" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D224">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E224">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F224">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="G224">
-        <v>65</v>
+        <v>166</v>
       </c>
       <c r="H224">
-        <v>0.84615384615384603</v>
+        <v>0.81927710843373502</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B225">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="C225" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D225">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="E225">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F225">
-        <v>1</v>
+        <v>236</v>
       </c>
       <c r="G225">
-        <v>66</v>
+        <v>183</v>
       </c>
       <c r="H225">
-        <v>0.84848484848484795</v>
+        <v>0.72131147540983598</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B226">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C226" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D226">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E226">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="F226">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="G226">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="H226">
-        <v>0.81690140845070403</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B227">
         <v>2024</v>
       </c>
       <c r="C227" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D227">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E227">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G227">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="H227">
-        <v>0.83333333333333404</v>
+        <v>0.648484848484848</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B228">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C228" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D228">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E228">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="G228">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="H228">
-        <v>0.88461538461538403</v>
+        <v>0.73291925465838503</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B229">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C229" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D229">
         <v>0</v>
       </c>
       <c r="E229">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="F229">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>0.77464788732394396</v>
       </c>
     </row>
   </sheetData>
@@ -7377,10 +7381,10 @@
         <v>188</v>
       </c>
       <c r="D2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E2">
-        <v>0.43085106382978722</v>
+        <v>0.43617021276595747</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -7394,10 +7398,10 @@
         <v>151</v>
       </c>
       <c r="D3">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3">
-        <v>0.49006622516556292</v>
+        <v>0.50331125827814571</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -7411,10 +7415,10 @@
         <v>162</v>
       </c>
       <c r="D4">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4">
-        <v>0.49382716049382713</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7428,10 +7432,10 @@
         <v>134</v>
       </c>
       <c r="D5">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5">
-        <v>0.42537313432835822</v>
+        <v>0.43283582089552236</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7445,10 +7449,10 @@
         <v>137</v>
       </c>
       <c r="D6">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E6">
-        <v>0.44525547445255476</v>
+        <v>0.40875912408759124</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -7479,10 +7483,10 @@
         <v>116</v>
       </c>
       <c r="D8">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E8">
-        <v>0.5</v>
+        <v>0.51724137931034486</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -7496,10 +7500,10 @@
         <v>128</v>
       </c>
       <c r="D9">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E9">
-        <v>0.6328125</v>
+        <v>0.6484375</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -7513,10 +7517,10 @@
         <v>112</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E10">
-        <v>0.5803571428571429</v>
+        <v>0.5892857142857143</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -7530,10 +7534,10 @@
         <v>130</v>
       </c>
       <c r="D11">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E11">
-        <v>0.55384615384615388</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -7598,10 +7602,10 @@
         <v>116</v>
       </c>
       <c r="D15">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15">
-        <v>0.59482758620689657</v>
+        <v>0.61206896551724133</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -7615,10 +7619,10 @@
         <v>144</v>
       </c>
       <c r="D16">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E16">
-        <v>0.59722222222222221</v>
+        <v>0.4861111111111111</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -7666,10 +7670,10 @@
         <v>502</v>
       </c>
       <c r="D19">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E19">
-        <v>0.49003984063745021</v>
+        <v>0.49203187250996017</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -7683,10 +7687,10 @@
         <v>548</v>
       </c>
       <c r="D20">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>0.51277372262773724</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -7700,10 +7704,10 @@
         <v>659</v>
       </c>
       <c r="D21">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="E21">
-        <v>0.47040971168437024</v>
+        <v>0.51896813353566007</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -7751,10 +7755,10 @@
         <v>260</v>
       </c>
       <c r="D24">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E24">
-        <v>0.38076923076923075</v>
+        <v>0.38846153846153847</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -7768,10 +7772,10 @@
         <v>263</v>
       </c>
       <c r="D25">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E25">
-        <v>0.36501901140684412</v>
+        <v>0.38022813688212925</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -7782,13 +7786,13 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D26">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="E26">
-        <v>0.36148648648648651</v>
+        <v>0.47474747474747475</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/data_corp_demo.xlsx
+++ b/src/pages/data/data_corp_demo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/corporate_project/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0C2838B-BCD0-4CA9-AB34-DEAFEA167CFB}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="11_AD4D2F04E46CFB4ACB3E20AB0D56E536693EDF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF7051B1-0EFF-45E5-BDCF-3F6080ED43BA}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_corp" sheetId="1" r:id="rId1"/>
@@ -483,9 +483,9 @@
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" customWidth="1"/>
     <col min="7" max="7" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2792,10 +2792,10 @@
         <v>35</v>
       </c>
       <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89">
         <v>20</v>
-      </c>
-      <c r="F89">
-        <v>2</v>
       </c>
       <c r="G89">
         <v>43</v>
@@ -2818,10 +2818,10 @@
         <v>40</v>
       </c>
       <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
         <v>16</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
       </c>
       <c r="G90">
         <v>59</v>
@@ -2844,10 +2844,10 @@
         <v>57</v>
       </c>
       <c r="E91">
+        <v>2</v>
+      </c>
+      <c r="F91">
         <v>15</v>
-      </c>
-      <c r="F91">
-        <v>2</v>
       </c>
       <c r="G91">
         <v>74</v>
@@ -2870,10 +2870,10 @@
         <v>56</v>
       </c>
       <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92">
         <v>10</v>
-      </c>
-      <c r="F92">
-        <v>1</v>
       </c>
       <c r="G92">
         <v>69</v>
@@ -2896,10 +2896,10 @@
         <v>55</v>
       </c>
       <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
         <v>16</v>
-      </c>
-      <c r="F93">
-        <v>0</v>
       </c>
       <c r="G93">
         <v>65</v>
@@ -2922,10 +2922,10 @@
         <v>55</v>
       </c>
       <c r="E94">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F94">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="G94">
         <v>66</v>
@@ -2948,10 +2948,10 @@
         <v>58</v>
       </c>
       <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
         <v>28</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
       </c>
       <c r="G95">
         <v>71</v>
@@ -2974,10 +2974,10 @@
         <v>75</v>
       </c>
       <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
         <v>14</v>
-      </c>
-      <c r="F96">
-        <v>0</v>
       </c>
       <c r="G96">
         <v>90</v>
@@ -3000,10 +3000,10 @@
         <v>22</v>
       </c>
       <c r="E97">
+        <v>1</v>
+      </c>
+      <c r="F97">
         <v>11</v>
-      </c>
-      <c r="F97">
-        <v>1</v>
       </c>
       <c r="G97">
         <v>26</v>
@@ -3046,22 +3046,22 @@
         <v>2025</v>
       </c>
       <c r="C99" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D99">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G99">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="H99">
-        <v>0.91228070175438603</v>
+        <v>0.86486486486486502</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -3072,22 +3072,22 @@
         <v>2025</v>
       </c>
       <c r="C100" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D100">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E100">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F100">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G100">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H100">
-        <v>0.82142857142857095</v>
+        <v>0.91228070175438603</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -3098,22 +3098,22 @@
         <v>2025</v>
       </c>
       <c r="C101" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D101">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G101">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H101">
-        <v>0.86486486486486502</v>
+        <v>0.84507042253521103</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -3124,22 +3124,22 @@
         <v>2025</v>
       </c>
       <c r="C102" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D102">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E102">
         <v>0</v>
       </c>
       <c r="F102">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G102">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="H102">
-        <v>0.89552238805970197</v>
+        <v>0.82142857142857095</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -3150,7 +3150,7 @@
         <v>2025</v>
       </c>
       <c r="C103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D103">
         <v>60</v>
@@ -3159,13 +3159,13 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G103">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H103">
-        <v>0.84507042253521103</v>
+        <v>0.89552238805970197</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -3176,22 +3176,22 @@
         <v>2025</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D104">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E104">
         <v>1</v>
       </c>
       <c r="F104">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G104">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H104">
-        <v>0.85135135135135098</v>
+        <v>0.88372093023255804</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -3202,22 +3202,22 @@
         <v>2025</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D105">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E105">
         <v>1</v>
       </c>
       <c r="F105">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G105">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H105">
-        <v>0.88372093023255804</v>
+        <v>0.85135135135135098</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -3254,22 +3254,22 @@
         <v>2026</v>
       </c>
       <c r="C107" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D107">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="E107">
         <v>0</v>
       </c>
       <c r="F107">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G107">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H107">
-        <v>0.89473684210526305</v>
+        <v>0.83636363636363598</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -3280,22 +3280,22 @@
         <v>2026</v>
       </c>
       <c r="C108" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108">
+        <v>68</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
         <v>16</v>
       </c>
-      <c r="D108">
-        <v>62</v>
-      </c>
-      <c r="E108">
-        <v>3</v>
-      </c>
-      <c r="F108">
-        <v>21</v>
-      </c>
       <c r="G108">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H108">
-        <v>0.92857142857142905</v>
+        <v>0.89473684210526305</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -3306,22 +3306,22 @@
         <v>2026</v>
       </c>
       <c r="C109" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D109">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="E109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="G109">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="H109">
-        <v>0.95081967213114804</v>
+        <v>0.94736842105263197</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -3332,22 +3332,22 @@
         <v>2026</v>
       </c>
       <c r="C110" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D110">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F110">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G110">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H110">
-        <v>0.91666666666666596</v>
+        <v>0.92857142857142905</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -3384,22 +3384,22 @@
         <v>2026</v>
       </c>
       <c r="C112" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D112">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G112">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="H112">
-        <v>0.94736842105263197</v>
+        <v>0.95081967213114804</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -3410,22 +3410,22 @@
         <v>2026</v>
       </c>
       <c r="C113" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D113">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G113">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H113">
-        <v>0.87654320987654299</v>
+        <v>0.91666666666666596</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -3436,22 +3436,22 @@
         <v>2026</v>
       </c>
       <c r="C114" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D114">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114">
         <v>18</v>
       </c>
       <c r="G114">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="H114">
-        <v>0.83636363636363598</v>
+        <v>0.87654320987654299</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -3572,10 +3572,10 @@
         <v>0</v>
       </c>
       <c r="E119">
+        <v>1</v>
+      </c>
+      <c r="F119">
         <v>47</v>
-      </c>
-      <c r="F119">
-        <v>1</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -5204,22 +5204,22 @@
         <v>2021</v>
       </c>
       <c r="C182" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D182">
-        <v>300</v>
+        <v>147</v>
       </c>
       <c r="E182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182">
-        <v>34</v>
+        <v>177</v>
       </c>
       <c r="G182">
-        <v>319</v>
+        <v>205</v>
       </c>
       <c r="H182">
-        <v>0.94357366771159878</v>
+        <v>0.71707317073170729</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
@@ -5230,22 +5230,22 @@
         <v>2021</v>
       </c>
       <c r="C183" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D183">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="E183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G183">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="H183">
-        <v>0.89508196721311473</v>
+        <v>0.94357366771159878</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -5256,22 +5256,22 @@
         <v>2021</v>
       </c>
       <c r="C184" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D184">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="E184">
         <v>0</v>
       </c>
       <c r="F184">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G184">
-        <v>257</v>
+        <v>305</v>
       </c>
       <c r="H184">
-        <v>0.96498054474708173</v>
+        <v>0.89508196721311473</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -5279,25 +5279,25 @@
         <v>20</v>
       </c>
       <c r="B185">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C185" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D185">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E185">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F185">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="G185">
-        <v>324</v>
+        <v>257</v>
       </c>
       <c r="H185">
-        <v>0.81481481481481477</v>
+        <v>0.96498054474708173</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -5308,22 +5308,22 @@
         <v>2022</v>
       </c>
       <c r="C186" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D186">
-        <v>275</v>
+        <v>115</v>
       </c>
       <c r="E186">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F186">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="G186">
-        <v>297</v>
+        <v>202</v>
       </c>
       <c r="H186">
-        <v>0.93602693602693599</v>
+        <v>0.60396039603960394</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -5334,22 +5334,22 @@
         <v>2022</v>
       </c>
       <c r="C187" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D187">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="E187">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F187">
         <v>34</v>
       </c>
       <c r="G187">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="H187">
-        <v>0.84776119402985073</v>
+        <v>0.81481481481481477</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -5357,25 +5357,25 @@
         <v>20</v>
       </c>
       <c r="B188">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C188" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D188">
-        <v>195</v>
+        <v>280</v>
       </c>
       <c r="E188">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F188">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G188">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="H188">
-        <v>0.71480144404332135</v>
+        <v>0.84776119402985073</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
@@ -5383,25 +5383,25 @@
         <v>20</v>
       </c>
       <c r="B189">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C189" t="s">
         <v>23</v>
       </c>
       <c r="D189">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="E189">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F189">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="G189">
-        <v>318</v>
+        <v>297</v>
       </c>
       <c r="H189">
-        <v>0.9088050314465409</v>
+        <v>0.93602693602693599</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
@@ -5412,22 +5412,22 @@
         <v>2023</v>
       </c>
       <c r="C190" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D190">
-        <v>243</v>
+        <v>107</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F190">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="G190">
-        <v>298</v>
+        <v>195</v>
       </c>
       <c r="H190">
-        <v>0.81543624161073824</v>
+        <v>0.57948717948717954</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
@@ -5435,25 +5435,25 @@
         <v>20</v>
       </c>
       <c r="B191">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C191" t="s">
         <v>21</v>
       </c>
       <c r="D191">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="E191">
         <v>3</v>
       </c>
       <c r="F191">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="G191">
-        <v>227</v>
+        <v>277</v>
       </c>
       <c r="H191">
-        <v>0.77533039647577096</v>
+        <v>0.71480144404332135</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
@@ -5461,25 +5461,25 @@
         <v>20</v>
       </c>
       <c r="B192">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C192" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D192">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="E192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F192">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G192">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="H192">
-        <v>0.94117647058823528</v>
+        <v>0.81543624161073824</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
@@ -5487,25 +5487,25 @@
         <v>20</v>
       </c>
       <c r="B193">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C193" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D193">
-        <v>196</v>
+        <v>289</v>
       </c>
       <c r="E193">
         <v>0</v>
       </c>
       <c r="F193">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="G193">
-        <v>227</v>
+        <v>318</v>
       </c>
       <c r="H193">
-        <v>0.86343612334801767</v>
+        <v>0.9088050314465409</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -5513,25 +5513,25 @@
         <v>20</v>
       </c>
       <c r="B194">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C194" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D194">
-        <v>251</v>
+        <v>132</v>
       </c>
       <c r="E194">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F194">
-        <v>65</v>
+        <v>176</v>
       </c>
       <c r="G194">
-        <v>313</v>
+        <v>208</v>
       </c>
       <c r="H194">
-        <v>0.81150159744408945</v>
+        <v>0.65865384615384615</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
@@ -5539,25 +5539,25 @@
         <v>20</v>
       </c>
       <c r="B195">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C195" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D195">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F195">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G195">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H195">
-        <v>0.80973451327433632</v>
+        <v>0.77533039647577096</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
@@ -5565,25 +5565,25 @@
         <v>20</v>
       </c>
       <c r="B196">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C196" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D196">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="E196">
         <v>0</v>
       </c>
       <c r="F196">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="G196">
-        <v>251</v>
+        <v>227</v>
       </c>
       <c r="H196">
-        <v>0.91633466135458164</v>
+        <v>0.86343612334801767</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -5591,25 +5591,25 @@
         <v>20</v>
       </c>
       <c r="B197">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C197" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D197">
-        <v>292</v>
+        <v>255</v>
       </c>
       <c r="E197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F197">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="G197">
-        <v>351</v>
+        <v>272</v>
       </c>
       <c r="H197">
-        <v>0.84045584045584043</v>
+        <v>0.94117647058823528</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -5617,25 +5617,25 @@
         <v>20</v>
       </c>
       <c r="B198">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C198" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D198">
-        <v>285</v>
+        <v>137</v>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F198">
-        <v>25</v>
+        <v>210</v>
       </c>
       <c r="G198">
-        <v>319</v>
+        <v>189</v>
       </c>
       <c r="H198">
-        <v>0.89655172413793105</v>
+        <v>0.74603174603174605</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -5643,25 +5643,25 @@
         <v>20</v>
       </c>
       <c r="B199">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C199" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D199">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="E199">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F199">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="G199">
-        <v>220</v>
+        <v>313</v>
       </c>
       <c r="H199">
-        <v>0.95454545454545459</v>
+        <v>0.81150159744408945</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -5669,25 +5669,25 @@
         <v>20</v>
       </c>
       <c r="B200">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C200" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="E200">
         <v>0</v>
       </c>
       <c r="F200">
-        <v>324</v>
+        <v>37</v>
       </c>
       <c r="G200">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="H200">
-        <v>0.71707317073170729</v>
+        <v>0.80973451327433632</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -5695,25 +5695,25 @@
         <v>20</v>
       </c>
       <c r="B201">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="C201" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="E201">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F201">
-        <v>270</v>
+        <v>5</v>
       </c>
       <c r="G201">
-        <v>202</v>
+        <v>251</v>
       </c>
       <c r="H201">
-        <v>0.60396039603960394</v>
+        <v>0.91633466135458164</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -5721,25 +5721,25 @@
         <v>20</v>
       </c>
       <c r="B202">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C202" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="E202">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F202">
-        <v>221</v>
+        <v>43</v>
       </c>
       <c r="G202">
-        <v>195</v>
+        <v>351</v>
       </c>
       <c r="H202">
-        <v>0.57948717948717954</v>
+        <v>0.84045584045584043</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -5747,25 +5747,25 @@
         <v>20</v>
       </c>
       <c r="B203">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C203" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="E203">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F203">
-        <v>308</v>
+        <v>25</v>
       </c>
       <c r="G203">
-        <v>208</v>
+        <v>319</v>
       </c>
       <c r="H203">
-        <v>0.65865384615384615</v>
+        <v>0.89655172413793105</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -5773,25 +5773,25 @@
         <v>20</v>
       </c>
       <c r="B204">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C204" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="E204">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F204">
-        <v>347</v>
+        <v>7</v>
       </c>
       <c r="G204">
-        <v>189</v>
+        <v>220</v>
       </c>
       <c r="H204">
-        <v>0.74603174603174605</v>
+        <v>0.95454545454545459</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -5805,13 +5805,13 @@
         <v>24</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="E205">
         <v>12</v>
       </c>
       <c r="F205">
-        <v>407</v>
+        <v>285</v>
       </c>
       <c r="G205">
         <v>184</v>
@@ -5828,22 +5828,22 @@
         <v>2021</v>
       </c>
       <c r="C206" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D206">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="E206">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F206">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="G206">
-        <v>221</v>
+        <v>166</v>
       </c>
       <c r="H206">
-        <v>0.92307692307692302</v>
+        <v>0.81927710843373502</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -5854,22 +5854,22 @@
         <v>2021</v>
       </c>
       <c r="C207" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D207">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E207">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F207">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G207">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="H207">
-        <v>0.90987124463519298</v>
+        <v>0.92307692307692302</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -5880,22 +5880,22 @@
         <v>2021</v>
       </c>
       <c r="C208" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D208">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E208">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F208">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G208">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="H208">
-        <v>0.91780821917808197</v>
+        <v>0.90987124463519298</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
@@ -5903,25 +5903,25 @@
         <v>25</v>
       </c>
       <c r="B209">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C209" t="s">
         <v>23</v>
       </c>
       <c r="D209">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E209">
         <v>0</v>
       </c>
       <c r="F209">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G209">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="H209">
-        <v>0.91228070175438603</v>
+        <v>0.91780821917808197</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -5932,22 +5932,22 @@
         <v>2022</v>
       </c>
       <c r="C210" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D210">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="E210">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F210">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="G210">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="H210">
-        <v>0.80930232558139503</v>
+        <v>0.72131147540983598</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -5958,22 +5958,22 @@
         <v>2022</v>
       </c>
       <c r="C211" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D211">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F211">
         <v>27</v>
       </c>
       <c r="G211">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H211">
-        <v>0.78341013824884798</v>
+        <v>0.80930232558139503</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -5981,25 +5981,25 @@
         <v>25</v>
       </c>
       <c r="B212">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C212" t="s">
         <v>22</v>
       </c>
       <c r="D212">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F212">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G212">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="H212">
-        <v>0.82587064676616895</v>
+        <v>0.78341013824884798</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -6007,25 +6007,25 @@
         <v>25</v>
       </c>
       <c r="B213">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C213" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D213">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="E213">
         <v>0</v>
       </c>
       <c r="F213">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="G213">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="H213">
-        <v>0.79916317991631802</v>
+        <v>0.91228070175438603</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
@@ -6036,22 +6036,22 @@
         <v>2023</v>
       </c>
       <c r="C214" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D214">
-        <v>187</v>
+        <v>93</v>
       </c>
       <c r="E214">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F214">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="G214">
-        <v>197</v>
+        <v>140</v>
       </c>
       <c r="H214">
-        <v>0.949238578680203</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -6059,25 +6059,25 @@
         <v>25</v>
       </c>
       <c r="B215">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C215" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D215">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="E215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F215">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="G215">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="H215">
-        <v>0.93034825870646798</v>
+        <v>0.79916317991631802</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -6085,25 +6085,25 @@
         <v>25</v>
       </c>
       <c r="B216">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C216" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D216">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="E216">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F216">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G216">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="H216">
-        <v>0.79444444444444395</v>
+        <v>0.82587064676616895</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
@@ -6111,25 +6111,25 @@
         <v>25</v>
       </c>
       <c r="B217">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C217" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D217">
         <v>187</v>
       </c>
       <c r="E217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F217">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="G217">
-        <v>234</v>
+        <v>197</v>
       </c>
       <c r="H217">
-        <v>0.80341880341880401</v>
+        <v>0.949238578680203</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -6137,25 +6137,25 @@
         <v>25</v>
       </c>
       <c r="B218">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C218" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D218">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="E218">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F218">
-        <v>50</v>
+        <v>97</v>
       </c>
       <c r="G218">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="H218">
-        <v>0.82352941176470595</v>
+        <v>0.648484848484848</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -6163,25 +6163,25 @@
         <v>25</v>
       </c>
       <c r="B219">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C219" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D219">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="E219">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F219">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="G219">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H219">
-        <v>0.86592178770949702</v>
+        <v>0.79444444444444395</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
@@ -6189,25 +6189,25 @@
         <v>25</v>
       </c>
       <c r="B220">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C220" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D220">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="E220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G220">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="H220">
-        <v>0.93273542600896897</v>
+        <v>0.80341880341880401</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -6215,25 +6215,25 @@
         <v>25</v>
       </c>
       <c r="B221">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="C221" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D221">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F221">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="G221">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="H221">
-        <v>0.85096153846153799</v>
+        <v>0.93034825870646798</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -6241,25 +6241,25 @@
         <v>25</v>
       </c>
       <c r="B222">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C222" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D222">
-        <v>191</v>
+        <v>118</v>
       </c>
       <c r="E222">
         <v>0</v>
       </c>
       <c r="F222">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="G222">
-        <v>214</v>
+        <v>161</v>
       </c>
       <c r="H222">
-        <v>0.89252336448598102</v>
+        <v>0.73291925465838503</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
@@ -6267,25 +6267,25 @@
         <v>25</v>
       </c>
       <c r="B223">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C223" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D223">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="E223">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F223">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G223">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="H223">
-        <v>0.92201834862385301</v>
+        <v>0.82352941176470595</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
@@ -6293,25 +6293,25 @@
         <v>25</v>
       </c>
       <c r="B224">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="C224" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="E224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F224">
-        <v>212</v>
+        <v>59</v>
       </c>
       <c r="G224">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="H224">
-        <v>0.81927710843373502</v>
+        <v>0.86592178770949702</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
@@ -6319,25 +6319,25 @@
         <v>25</v>
       </c>
       <c r="B225">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="C225" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D225">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="E225">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F225">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="G225">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="H225">
-        <v>0.72131147540983598</v>
+        <v>0.93273542600896897</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -6345,25 +6345,25 @@
         <v>25</v>
       </c>
       <c r="B226">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="C226" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="E226">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F226">
-        <v>175</v>
+        <v>40</v>
       </c>
       <c r="G226">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="H226">
-        <v>0.7</v>
+        <v>0.85096153846153799</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
@@ -6371,25 +6371,25 @@
         <v>25</v>
       </c>
       <c r="B227">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C227" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D227">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="E227">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F227">
-        <v>201</v>
+        <v>8</v>
       </c>
       <c r="G227">
-        <v>165</v>
+        <v>214</v>
       </c>
       <c r="H227">
-        <v>0.648484848484848</v>
+        <v>0.89252336448598102</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -6397,25 +6397,25 @@
         <v>25</v>
       </c>
       <c r="B228">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C228" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F228">
-        <v>208</v>
+        <v>41</v>
       </c>
       <c r="G228">
-        <v>161</v>
+        <v>218</v>
       </c>
       <c r="H228">
-        <v>0.73291925465838503</v>
+        <v>0.92201834862385301</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -6429,13 +6429,13 @@
         <v>24</v>
       </c>
       <c r="D229">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="E229">
         <v>2</v>
       </c>
       <c r="F229">
-        <v>255</v>
+        <v>147</v>
       </c>
       <c r="G229">
         <v>142</v>
